--- a/artfynd/A 4810-2026 artfynd.xlsx
+++ b/artfynd/A 4810-2026 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>136439637</v>
       </c>
       <c r="B3" t="n">
-        <v>110322</v>
+        <v>110325</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1017,7 +1017,7 @@
         <v>136439638</v>
       </c>
       <c r="B5" t="n">
-        <v>106395</v>
+        <v>106398</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 4810-2026 artfynd.xlsx
+++ b/artfynd/A 4810-2026 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>136439637</v>
       </c>
       <c r="B3" t="n">
-        <v>110325</v>
+        <v>110326</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1017,7 +1017,7 @@
         <v>136439638</v>
       </c>
       <c r="B5" t="n">
-        <v>106398</v>
+        <v>106399</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 4810-2026 artfynd.xlsx
+++ b/artfynd/A 4810-2026 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>136439637</v>
       </c>
       <c r="B3" t="n">
-        <v>110326</v>
+        <v>110331</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1017,7 +1017,7 @@
         <v>136439638</v>
       </c>
       <c r="B5" t="n">
-        <v>106399</v>
+        <v>106404</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 4810-2026 artfynd.xlsx
+++ b/artfynd/A 4810-2026 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>136439637</v>
       </c>
       <c r="B3" t="n">
-        <v>110331</v>
+        <v>110333</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1017,7 +1017,7 @@
         <v>136439638</v>
       </c>
       <c r="B5" t="n">
-        <v>106404</v>
+        <v>106406</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 4810-2026 artfynd.xlsx
+++ b/artfynd/A 4810-2026 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>136439637</v>
       </c>
       <c r="B3" t="n">
-        <v>110333</v>
+        <v>110339</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1017,7 +1017,7 @@
         <v>136439638</v>
       </c>
       <c r="B5" t="n">
-        <v>106406</v>
+        <v>106412</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 4810-2026 artfynd.xlsx
+++ b/artfynd/A 4810-2026 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>136439637</v>
       </c>
       <c r="B3" t="n">
-        <v>110339</v>
+        <v>110341</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1017,7 +1017,7 @@
         <v>136439638</v>
       </c>
       <c r="B5" t="n">
-        <v>106412</v>
+        <v>106414</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 4810-2026 artfynd.xlsx
+++ b/artfynd/A 4810-2026 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>136439637</v>
       </c>
       <c r="B3" t="n">
-        <v>110341</v>
+        <v>110342</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1017,7 +1017,7 @@
         <v>136439638</v>
       </c>
       <c r="B5" t="n">
-        <v>106414</v>
+        <v>106415</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
